--- a/output/pdf_financials_xlsx/KIRO.xlsx
+++ b/output/pdf_financials_xlsx/KIRO.xlsx
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.146427</v>
       </c>
     </row>
     <row r="119">
@@ -3110,7 +3110,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KIRO.xlsx
+++ b/output/pdf_financials_xlsx/KIRO.xlsx
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011648</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.415146</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.011648</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.415146</v>
       </c>
     </row>
     <row r="37">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.211141</v>
+        <v>0.199493</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.606726</v>
+        <v>0.19158</v>
       </c>
     </row>
     <row r="49">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/KIRO.xlsx
+++ b/output/pdf_financials_xlsx/KIRO.xlsx
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002792</v>
       </c>
     </row>
     <row r="102">
@@ -1818,7 +1818,7 @@
         <v>0.016148</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.205144</v>
+        <v>0.202352</v>
       </c>
     </row>
     <row r="107">
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.021256</v>
       </c>
     </row>
     <row r="111">
@@ -2930,7 +2930,11 @@
           <t>Accretion 6</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -2984,7 +2988,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
